--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6807.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6807.xlsx
@@ -1292,6 +1292,18 @@
       <c r="F15" t="n">
         <v>0.438</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.438</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>6807-04-04-NWO-FG</t>
@@ -1304,12 +1316,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-04-04-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-04-04-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1337,6 +1349,18 @@
       <c r="F16" t="n">
         <v>0.75</v>
       </c>
+      <c r="G16" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5620000000000001</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>6807-08-06-NWO-FG</t>
@@ -1349,12 +1373,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-06-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-06-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1382,6 +1406,18 @@
       <c r="F17" t="n">
         <v>0.75</v>
       </c>
+      <c r="G17" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.75</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>6807-08-08-NWO-FG</t>
@@ -1394,12 +1430,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-08-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-08-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1427,6 +1463,18 @@
       <c r="F18" t="n">
         <v>1.062</v>
       </c>
+      <c r="G18" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.062</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>6807-12-12-NWO-FG</t>
@@ -1439,12 +1487,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-12-12-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-12-12-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6807.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6807.xlsx
@@ -1289,6 +1289,18 @@
           <t>6807-04-04-NWO-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5629999999999999</v>
+      </c>
       <c r="F15" t="n">
         <v>0.438</v>
       </c>
@@ -1311,17 +1323,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-04-04-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-04-04-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1346,6 +1358,18 @@
           <t>6807-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="F16" t="n">
         <v>0.75</v>
       </c>
@@ -1368,17 +1392,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-06-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-06-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1403,6 +1427,18 @@
           <t>6807-08-08-NWO-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.875</v>
+      </c>
       <c r="F17" t="n">
         <v>0.75</v>
       </c>
@@ -1425,17 +1461,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-08-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-08-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1460,6 +1496,18 @@
           <t>6807-12-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F18" t="n">
         <v>1.062</v>
       </c>
@@ -1482,17 +1530,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-12-12-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-12-12-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
